--- a/AAII_Financials/Yearly/ST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ST_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>271800</v>
+        <v>274600</v>
       </c>
       <c r="E14" s="3">
         <v>353000</v>
@@ -1251,7 +1251,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-23000</v>
+        <v>-25800</v>
       </c>
       <c r="E20" s="3">
         <v>-5200</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>605300</v>
+        <v>608100</v>
       </c>
       <c r="E21" s="3">
         <v>616900</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23000</v>
+        <v>25800</v>
       </c>
       <c r="E32" s="3">
         <v>5200</v>
@@ -2276,7 +2276,7 @@
         <v>744100</v>
       </c>
       <c r="G43" s="3">
-        <v>742100</v>
+        <v>742400</v>
       </c>
       <c r="H43" s="3">
         <v>653400</v>
@@ -2327,7 +2327,7 @@
         <v>713500</v>
       </c>
       <c r="G44" s="3">
-        <v>643900</v>
+        <v>644900</v>
       </c>
       <c r="H44" s="3">
         <v>588200</v>
@@ -2426,10 +2426,10 @@
         <v>2027200</v>
       </c>
       <c r="F46" s="3">
-        <v>2101800</v>
+        <v>2102400</v>
       </c>
       <c r="G46" s="3">
-        <v>2772400</v>
+        <v>2775000</v>
       </c>
       <c r="H46" s="3">
         <v>3077000</v>
@@ -2477,10 +2477,10 @@
         <v>6100</v>
       </c>
       <c r="F47" s="3">
-        <v>22900</v>
+        <v>18300</v>
       </c>
       <c r="G47" s="3">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="H47" s="3">
         <v>65000</v>
@@ -2528,10 +2528,10 @@
         <v>859500</v>
       </c>
       <c r="F48" s="3">
-        <v>920800</v>
+        <v>926200</v>
       </c>
       <c r="G48" s="3">
-        <v>877500</v>
+        <v>883700</v>
       </c>
       <c r="H48" s="3">
         <v>865100</v>
@@ -2579,10 +2579,10 @@
         <v>3876700</v>
       </c>
       <c r="F49" s="3">
-        <v>4423000</v>
+        <v>4426400</v>
       </c>
       <c r="G49" s="3">
-        <v>5096300</v>
+        <v>4910900</v>
       </c>
       <c r="H49" s="3">
         <v>4448800</v>
@@ -2732,10 +2732,10 @@
         <v>85600</v>
       </c>
       <c r="F52" s="3">
-        <v>55400</v>
+        <v>76100</v>
       </c>
       <c r="G52" s="3">
-        <v>48500</v>
+        <v>71000</v>
       </c>
       <c r="H52" s="3">
         <v>52900</v>
@@ -2834,10 +2834,10 @@
         <v>7143300</v>
       </c>
       <c r="F54" s="3">
-        <v>7772000</v>
+        <v>7681000</v>
       </c>
       <c r="G54" s="3">
-        <v>8917900</v>
+        <v>8756200</v>
       </c>
       <c r="H54" s="3">
         <v>8613800</v>
@@ -2930,7 +2930,7 @@
         <v>482300</v>
       </c>
       <c r="G57" s="3">
-        <v>532000</v>
+        <v>531600</v>
       </c>
       <c r="H57" s="3">
         <v>459100</v>
@@ -2978,10 +2978,10 @@
         <v>15500</v>
       </c>
       <c r="F58" s="3">
-        <v>14100</v>
+        <v>13700</v>
       </c>
       <c r="G58" s="3">
-        <v>266800</v>
+        <v>266400</v>
       </c>
       <c r="H58" s="3">
         <v>17900</v>
@@ -3029,10 +3029,10 @@
         <v>58300</v>
       </c>
       <c r="F59" s="3">
-        <v>71400</v>
+        <v>46800</v>
       </c>
       <c r="G59" s="3">
-        <v>93500</v>
+        <v>63300</v>
       </c>
       <c r="H59" s="3">
         <v>39300</v>
@@ -3080,10 +3080,10 @@
         <v>711400</v>
       </c>
       <c r="F60" s="3">
-        <v>825200</v>
+        <v>823700</v>
       </c>
       <c r="G60" s="3">
-        <v>1182900</v>
+        <v>1179000</v>
       </c>
       <c r="H60" s="3">
         <v>836300</v>
@@ -3131,10 +3131,10 @@
         <v>3242000</v>
       </c>
       <c r="F61" s="3">
-        <v>3427700</v>
+        <v>3426200</v>
       </c>
       <c r="G61" s="3">
-        <v>4016500</v>
+        <v>4016400</v>
       </c>
       <c r="H61" s="3">
         <v>4277300</v>
@@ -3182,10 +3182,10 @@
         <v>35900</v>
       </c>
       <c r="F62" s="3">
-        <v>34100</v>
+        <v>37500</v>
       </c>
       <c r="G62" s="3">
-        <v>46000</v>
+        <v>49400</v>
       </c>
       <c r="H62" s="3">
         <v>27500</v>
@@ -3386,10 +3386,10 @@
         <v>4252900</v>
       </c>
       <c r="F66" s="3">
-        <v>4698300</v>
+        <v>4684700</v>
       </c>
       <c r="G66" s="3">
-        <v>5680100</v>
+        <v>5645400</v>
       </c>
       <c r="H66" s="3">
         <v>5519000</v>
@@ -3662,10 +3662,10 @@
         <v>2340200</v>
       </c>
       <c r="F72" s="3">
-        <v>2262300</v>
+        <v>2295600</v>
       </c>
       <c r="G72" s="3">
-        <v>2398900</v>
+        <v>2383300</v>
       </c>
       <c r="H72" s="3">
         <v>2132300</v>
@@ -3866,10 +3866,10 @@
         <v>2890400</v>
       </c>
       <c r="F76" s="3">
-        <v>3073600</v>
+        <v>2996300</v>
       </c>
       <c r="G76" s="3">
-        <v>3237900</v>
+        <v>3110800</v>
       </c>
       <c r="H76" s="3">
         <v>3094700</v>
